--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_10.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03061126452671081</v>
+        <v>0.02612309564079044</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008451193563359072</v>
+        <v>0.008445755456178603</v>
       </c>
       <c r="C2" t="n">
-        <v>63630810</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63630810</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>43032758</v>
+        <v>4020826</v>
       </c>
       <c r="L2" t="n">
-        <v>22215713</v>
+        <v>1761805</v>
       </c>
       <c r="M2" t="n">
-        <v>5042159</v>
+        <v>322774</v>
       </c>
       <c r="N2" t="n">
-        <v>224830</v>
+        <v>7917</v>
       </c>
       <c r="O2" t="n">
-        <v>2979639</v>
+        <v>176945</v>
       </c>
       <c r="P2" t="n">
-        <v>1191963</v>
+        <v>46332</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999880194664001</v>
+        <v>0.9999644160270691</v>
       </c>
       <c r="R2" t="n">
-        <v>0.821766197681427</v>
+        <v>0.7353276610374451</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6762268543243408</v>
+        <v>0.5480805635452271</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5964923501014709</v>
+        <v>0.4294383227825165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.192735493183136</v>
+        <v>0.04628876969218254</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6548005342483521</v>
+        <v>0.4543633759021759</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7583422064781189</v>
+        <v>0.6199836730957031</v>
       </c>
       <c r="X2" t="n">
-        <v>63630810</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63630810</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>48394651</v>
+        <v>4789433</v>
       </c>
       <c r="AG2" t="n">
-        <v>30110592</v>
+        <v>3027015</v>
       </c>
       <c r="AH2" t="n">
-        <v>8040827</v>
+        <v>807060</v>
       </c>
       <c r="AI2" t="n">
-        <v>592793</v>
+        <v>59367</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4601871</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1802011</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559258222579956</v>
+        <v>0.9549785256385803</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116288423538208</v>
+        <v>0.912082850933075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.857900857925415</v>
+        <v>0.8579939603805542</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6614111065864563</v>
+        <v>0.6605360507965088</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019286632537842</v>
+        <v>0.90191650390625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314581155776978</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.007982894516103685</v>
+        <v>0.00666548745009604</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002024183214990091</v>
+        <v>0.002023579242838846</v>
       </c>
       <c r="C3" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>43032758</v>
+        <v>4020826</v>
       </c>
       <c r="E3" t="n">
-        <v>7219779</v>
+        <v>938134</v>
       </c>
       <c r="F3" t="n">
-        <v>243054</v>
+        <v>37218</v>
       </c>
       <c r="G3" t="n">
-        <v>29899</v>
+        <v>4099</v>
       </c>
       <c r="H3" t="n">
-        <v>16313</v>
+        <v>2526</v>
       </c>
       <c r="I3" t="n">
-        <v>1310</v>
+        <v>150</v>
       </c>
       <c r="J3" t="n">
-        <v>100960428</v>
+        <v>10069394</v>
       </c>
       <c r="K3" t="n">
-        <v>104715390</v>
+        <v>9965762</v>
       </c>
       <c r="L3" t="n">
-        <v>120858926</v>
+        <v>11634920</v>
       </c>
       <c r="M3" t="n">
-        <v>151797709</v>
+        <v>15044631</v>
       </c>
       <c r="N3" t="n">
-        <v>162753142</v>
+        <v>16162904</v>
       </c>
       <c r="O3" t="n">
-        <v>157915397</v>
+        <v>15691572</v>
       </c>
       <c r="P3" t="n">
-        <v>162276880</v>
+        <v>16193796</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8514057397842407</v>
+        <v>0.8036845922470093</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6712439656257629</v>
+        <v>0.5293272733688354</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5373468399047852</v>
+        <v>0.3424570560455322</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2505999505519867</v>
+        <v>0.08798817545175552</v>
       </c>
       <c r="V3" t="n">
-        <v>0.583580493927002</v>
+        <v>0.3456375598907471</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6159117817878723</v>
+        <v>0.2390650361776352</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>48394651</v>
+        <v>4789433</v>
       </c>
       <c r="Z3" t="n">
-        <v>1993417</v>
+        <v>198166</v>
       </c>
       <c r="AA3" t="n">
-        <v>85791</v>
+        <v>8476</v>
       </c>
       <c r="AB3" t="n">
-        <v>68679</v>
+        <v>6874</v>
       </c>
       <c r="AC3" t="n">
-        <v>348</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100961190</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>111817518</v>
+        <v>11187217</v>
       </c>
       <c r="AG3" t="n">
-        <v>128576818</v>
+        <v>12795836</v>
       </c>
       <c r="AH3" t="n">
-        <v>153876716</v>
+        <v>15339900</v>
       </c>
       <c r="AI3" t="n">
-        <v>163391371</v>
+        <v>16295512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>158985826</v>
+        <v>15853902</v>
       </c>
       <c r="AK3" t="n">
-        <v>162524116</v>
+        <v>16208926</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9574910998344421</v>
+        <v>0.957314133644104</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097864031791687</v>
+        <v>0.9094545841217041</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8569172024726868</v>
+        <v>0.8562752604484558</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6607387661933899</v>
+        <v>0.6597946286201477</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013046026229858</v>
+        <v>0.900970458984375</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311361312866211</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06896328242020383</v>
+        <v>0.06038637293192896</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03196319628040224</v>
+        <v>0.03194845442669837</v>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>8618746</v>
+        <v>1306683</v>
       </c>
       <c r="E4" t="n">
-        <v>22215713</v>
+        <v>1761805</v>
       </c>
       <c r="F4" t="n">
-        <v>1877768</v>
+        <v>203016</v>
       </c>
       <c r="G4" t="n">
-        <v>148361</v>
+        <v>25250</v>
       </c>
       <c r="H4" t="n">
-        <v>211028</v>
+        <v>28846</v>
       </c>
       <c r="I4" t="n">
-        <v>24674</v>
+        <v>2764</v>
       </c>
       <c r="J4" t="n">
-        <v>762</v>
+        <v>226</v>
       </c>
       <c r="K4" t="n">
-        <v>9333424</v>
+        <v>1447248</v>
       </c>
       <c r="L4" t="n">
-        <v>10636743</v>
+        <v>1452695</v>
       </c>
       <c r="M4" t="n">
-        <v>3410856</v>
+        <v>428845</v>
       </c>
       <c r="N4" t="n">
-        <v>941691</v>
+        <v>163118</v>
       </c>
       <c r="O4" t="n">
-        <v>1570814</v>
+        <v>212490</v>
       </c>
       <c r="P4" t="n">
-        <v>379838</v>
+        <v>28399</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999939799308777</v>
+        <v>0.9999821782112122</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8363234400749207</v>
+        <v>0.7679880857467651</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6737262010574341</v>
+        <v>0.5385407209396362</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5653769969940186</v>
+        <v>0.3810469210147858</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2178914695978165</v>
+        <v>0.06066364794969559</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6171425580978394</v>
+        <v>0.3926121890544891</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6797460913658142</v>
+        <v>0.3450710475444794</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2083830</v>
+        <v>211003</v>
       </c>
       <c r="Z4" t="n">
-        <v>30110592</v>
+        <v>3027015</v>
       </c>
       <c r="AA4" t="n">
-        <v>834124</v>
+        <v>83549</v>
       </c>
       <c r="AB4" t="n">
-        <v>55675</v>
+        <v>5619</v>
       </c>
       <c r="AC4" t="n">
-        <v>11430</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2231296</v>
+        <v>225793</v>
       </c>
       <c r="AG4" t="n">
-        <v>2918851</v>
+        <v>291779</v>
       </c>
       <c r="AH4" t="n">
-        <v>1331849</v>
+        <v>133576</v>
       </c>
       <c r="AI4" t="n">
-        <v>303462</v>
+        <v>30510</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500385</v>
+        <v>50160</v>
       </c>
       <c r="AK4" t="n">
-        <v>132602</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567078351974487</v>
+        <v>0.9561448693275452</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107067584991455</v>
+        <v>0.9107667803764343</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574087619781494</v>
+        <v>0.8571337461471558</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6610747575759888</v>
+        <v>0.6601651310920715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016165137290955</v>
+        <v>0.9014432430267334</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312970638275146</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>512176</v>
+        <v>104830</v>
       </c>
       <c r="E5" t="n">
-        <v>2754930</v>
+        <v>392509</v>
       </c>
       <c r="F5" t="n">
-        <v>5042159</v>
+        <v>322774</v>
       </c>
       <c r="G5" t="n">
-        <v>299028</v>
+        <v>43783</v>
       </c>
       <c r="H5" t="n">
-        <v>692587</v>
+        <v>70263</v>
       </c>
       <c r="I5" t="n">
-        <v>82484</v>
+        <v>8348</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7510428</v>
+        <v>982164</v>
       </c>
       <c r="L5" t="n">
-        <v>10880618</v>
+        <v>1566580</v>
       </c>
       <c r="M5" t="n">
-        <v>4341276</v>
+        <v>619750</v>
       </c>
       <c r="N5" t="n">
-        <v>672337</v>
+        <v>82061</v>
       </c>
       <c r="O5" t="n">
-        <v>2126150</v>
+        <v>334993</v>
       </c>
       <c r="P5" t="n">
-        <v>743319</v>
+        <v>147473</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999953508377075</v>
+        <v>0.9999862313270569</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8976629972457886</v>
+        <v>0.8520094752311707</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8692684769630432</v>
+        <v>0.8160772919654846</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9529009461402893</v>
+        <v>0.9361236095428467</v>
       </c>
       <c r="U5" t="n">
-        <v>0.990193784236908</v>
+        <v>0.9850646257400513</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9775386452674866</v>
+        <v>0.9666494131088257</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931761026382446</v>
+        <v>0.9892865419387817</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>81333</v>
+        <v>8141</v>
       </c>
       <c r="Z5" t="n">
-        <v>862543</v>
+        <v>87332</v>
       </c>
       <c r="AA5" t="n">
-        <v>8040827</v>
+        <v>807060</v>
       </c>
       <c r="AB5" t="n">
-        <v>100071</v>
+        <v>10049</v>
       </c>
       <c r="AC5" t="n">
-        <v>292331</v>
+        <v>29309</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2148535</v>
+        <v>213557</v>
       </c>
       <c r="AG5" t="n">
-        <v>2985739</v>
+        <v>301370</v>
       </c>
       <c r="AH5" t="n">
-        <v>1342608</v>
+        <v>135464</v>
       </c>
       <c r="AI5" t="n">
-        <v>304374</v>
+        <v>30611</v>
       </c>
       <c r="AJ5" t="n">
-        <v>503918</v>
+        <v>50697</v>
       </c>
       <c r="AK5" t="n">
-        <v>133271</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973389744758606</v>
+        <v>0.9732365012168884</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641258716583252</v>
+        <v>0.9638676047325134</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837509989738464</v>
+        <v>0.9836111068725586</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963070154190063</v>
+        <v>0.9962767362594604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938982129096985</v>
+        <v>0.9938561916351318</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983846545219421</v>
+        <v>0.9983761310577393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>150195</v>
+        <v>21236</v>
       </c>
       <c r="E6" t="n">
-        <v>201471</v>
+        <v>26745</v>
       </c>
       <c r="F6" t="n">
-        <v>214616</v>
+        <v>25471</v>
       </c>
       <c r="G6" t="n">
-        <v>224830</v>
+        <v>7917</v>
       </c>
       <c r="H6" t="n">
-        <v>93721</v>
+        <v>7732</v>
       </c>
       <c r="I6" t="n">
-        <v>12218</v>
+        <v>855</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65613</v>
+        <v>6613</v>
       </c>
       <c r="Z6" t="n">
-        <v>53974</v>
+        <v>5390</v>
       </c>
       <c r="AA6" t="n">
-        <v>109902</v>
+        <v>11097</v>
       </c>
       <c r="AB6" t="n">
-        <v>592793</v>
+        <v>59367</v>
       </c>
       <c r="AC6" t="n">
-        <v>70074</v>
+        <v>7030</v>
       </c>
       <c r="AD6" t="n">
-        <v>4811</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>204</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>49510</v>
+        <v>13636</v>
       </c>
       <c r="E7" t="n">
-        <v>418812</v>
+        <v>85531</v>
       </c>
       <c r="F7" t="n">
-        <v>989297</v>
+        <v>144340</v>
       </c>
       <c r="G7" t="n">
-        <v>409175</v>
+        <v>75155</v>
       </c>
       <c r="H7" t="n">
-        <v>2979639</v>
+        <v>176945</v>
       </c>
       <c r="I7" t="n">
-        <v>259152</v>
+        <v>16282</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8107</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>298715</v>
+        <v>30121</v>
       </c>
       <c r="AB7" t="n">
-        <v>76375</v>
+        <v>7701</v>
       </c>
       <c r="AC7" t="n">
-        <v>4601871</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120481</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>2797</v>
+        <v>863</v>
       </c>
       <c r="E8" t="n">
-        <v>41751</v>
+        <v>9776</v>
       </c>
       <c r="F8" t="n">
-        <v>86121</v>
+        <v>18800</v>
       </c>
       <c r="G8" t="n">
-        <v>55228</v>
+        <v>14831</v>
       </c>
       <c r="H8" t="n">
-        <v>557165</v>
+        <v>103123</v>
       </c>
       <c r="I8" t="n">
-        <v>1191963</v>
+        <v>46332</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3317</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2662</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126202</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1802011</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
